--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R3" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R4" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B6" t="n">
-        <v>97338</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R6" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>97338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R7" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R6" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R7" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R3" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B4" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R4" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R3" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R4" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R3" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B4" t="n">
-        <v>8444</v>
+        <v>58110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R4" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R6" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R7" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>132271541</v>
       </c>
       <c r="B4" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R3" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R4" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B6" t="n">
-        <v>97356</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R6" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>97357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R7" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R3" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B4" t="n">
-        <v>8444</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R4" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R6" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B7" t="n">
-        <v>97357</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R7" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271540</v>
+        <v>132271541</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634365</v>
+        <v>634380</v>
       </c>
       <c r="R3" t="n">
-        <v>6665726</v>
+        <v>6665707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271541</v>
+        <v>132271540</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634380</v>
+        <v>634365</v>
       </c>
       <c r="R4" t="n">
-        <v>6665707</v>
+        <v>6665726</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B6" t="n">
-        <v>97358</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R6" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R7" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>132271541</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>132271543</v>
       </c>
       <c r="B5" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>97362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R6" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B7" t="n">
-        <v>97361</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R7" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271549</v>
+        <v>132271548</v>
       </c>
       <c r="B6" t="n">
-        <v>97362</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634446</v>
+        <v>634521</v>
       </c>
       <c r="R6" t="n">
-        <v>6665983</v>
+        <v>6666162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271548</v>
+        <v>132271549</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>97362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634521</v>
+        <v>634446</v>
       </c>
       <c r="R7" t="n">
-        <v>6666162</v>
+        <v>6665983</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 8475-2022 artfynd.xlsx
+++ b/artfynd/A 8475-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132271542</v>
+        <v>132271543</v>
       </c>
       <c r="B2" t="n">
-        <v>8444</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634365</v>
+        <v>634478</v>
       </c>
       <c r="R2" t="n">
-        <v>6665673</v>
+        <v>6665516</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132271540</v>
+        <v>132271549</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634365</v>
+        <v>634446</v>
       </c>
       <c r="R3" t="n">
-        <v>6665726</v>
+        <v>6665983</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,48 +889,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132271541</v>
+        <v>122941428</v>
       </c>
       <c r="B4" t="n">
-        <v>58115</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barskalla, Upl</t>
+          <t>Järngården SO, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634380</v>
+        <v>634850</v>
       </c>
       <c r="R4" t="n">
-        <v>6665707</v>
+        <v>6665876</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,27 +962,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>2 korvar på toppen av stenblock</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,26 +993,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kanten av hygge</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132271543</v>
+        <v>132271541</v>
       </c>
       <c r="B5" t="n">
-        <v>97362</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634478</v>
+        <v>634380</v>
       </c>
       <c r="R5" t="n">
-        <v>6665516</v>
+        <v>6665707</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,32 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132271549</v>
+        <v>132271540</v>
       </c>
       <c r="B6" t="n">
-        <v>97362</v>
+        <v>8449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634446</v>
+        <v>634365</v>
       </c>
       <c r="R6" t="n">
-        <v>6665983</v>
+        <v>6665726</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132271548</v>
+        <v>132271542</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634521</v>
+        <v>634365</v>
       </c>
       <c r="R7" t="n">
-        <v>6666162</v>
+        <v>6665673</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,6 +1342,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132271548</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Barskalla, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>634521</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6666162</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
